--- a/business-libraries/test-data/learning_problem/tool.xlsx
+++ b/business-libraries/test-data/learning_problem/tool.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AJ8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,96 +430,102 @@
         <v>严重度*</v>
       </c>
       <c r="J1" t="str">
-        <v>对应归因*</v>
+        <v>对应归因编码*</v>
       </c>
       <c r="K1" t="str">
+        <v>对应归因名称</v>
+      </c>
+      <c r="L1" t="str">
         <v>工具标签*</v>
       </c>
-      <c r="L1" t="str">
-        <v>作用维度</v>
-      </c>
       <c r="M1" t="str">
+        <v>作用维度编码</v>
+      </c>
+      <c r="N1" t="str">
+        <v>效果说明</v>
+      </c>
+      <c r="O1" t="str">
         <v>操作步骤摘要*</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>关键话术</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>预期效果*</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>单次耗时</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>疗程与频次</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>重评间隔天数</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>禁止事项*</v>
       </c>
-      <c r="T1" t="str">
+      <c r="V1" t="str">
         <v>禁忌说明</v>
       </c>
-      <c r="U1" t="str">
+      <c r="W1" t="str">
         <v>前置工具编码</v>
       </c>
-      <c r="V1" t="str">
+      <c r="X1" t="str">
         <v>替代工具编码</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Y1" t="str">
         <v>进阶工具编码</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Z1" t="str">
         <v>证据等级*</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AA1" t="str">
         <v>证据来源</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AB1" t="str">
         <v>效果指标</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AC1" t="str">
         <v>失败标准</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AD1" t="str">
         <v>准备事项</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AE1" t="str">
         <v>所需材料</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AF1" t="str">
         <v>输出物</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AG1" t="str">
         <v>协同工具编码</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AH1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AI1" t="str">
         <v>版本*</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AJ1" t="str">
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
         <v>LP_RX_001</v>
       </c>
       <c r="B2" t="str">
-        <v>番茄工作法指导</v>
+        <v>一周学习行为观察表</v>
       </c>
       <c r="C2" t="str">
-        <v>番茄工作法</v>
+        <v>行为观察</v>
       </c>
       <c r="D2" t="str">
         <v>learning_problem</v>
       </c>
       <c r="E2" t="str">
-        <v>exercise</v>
+        <v>worksheet</v>
       </c>
       <c r="F2" t="str">
         <v>all</v>
@@ -528,102 +534,111 @@
         <v>teacher</v>
       </c>
       <c r="H2" t="str">
-        <v>感到情绪即将失控、疲惫难以恢复时</v>
+        <v>学习行为持续失序但原因不明时</v>
       </c>
       <c r="I2" t="str">
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>注意力与策略双重薄弱</v>
+        <v>LP_AT_BEHAVIOR</v>
       </c>
       <c r="K2" t="str">
-        <v>learning_problem,orange,focus</v>
+        <v>学习行为失序</v>
       </c>
       <c r="L2" t="str">
-        <v>情绪恢复</v>
+        <v>learning_problem,behavior</v>
       </c>
       <c r="M2" t="str">
-        <v>1) 离开当前情境 2) 三轮缓慢呼吸 3) 命名情绪 4) 选最小行动</v>
+        <v>LP_BEHAVIOR</v>
       </c>
       <c r="N2" t="str">
-        <v>现在先停三分钟，这三分钟只属于你自己。</v>
-      </c>
-      <c r="O2" t="str">
-        <v>单次可下降 1-2 分主观压力值</v>
+        <v>找出行为失序的具体模式和时段</v>
+      </c>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">连续五天记录课堂参与、作业完成和测验表现三项
+标出每天状态最好和最差的时段
+找出重复出现的模式，如某节课后必然分心
+针对最高频的模式做一次环境或任务调整</v>
       </c>
       <c r="P2" t="str">
-        <v>3 分钟</v>
+        <v>我注意到你在数学课的后半节特别容易走神，我们一起看看能怎么调整。</v>
       </c>
       <c r="Q2" t="str">
-        <v>每日 1-2 次，连续 7 天</v>
+        <v>识别出至少一个可干预的行为模式</v>
       </c>
       <c r="R2" t="str">
-        <v>7</v>
+        <v>每天 5 分钟</v>
       </c>
       <c r="S2" t="str">
-        <v>不用于替代危机处置；出现自伤念头或持续失眠时须转介心理专员</v>
+        <v>连续 5 天</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U2" t="str">
-        <v/>
+        <v>不要在记录期间同时改变多个变量</v>
       </c>
       <c r="V2" t="str">
         <v/>
       </c>
       <c r="W2" t="str">
-        <v>LP_RX_004</v>
+        <v/>
       </c>
       <c r="X2" t="str">
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y2" t="str">
-        <v>Kabat-Zinn 正念减压研究；教师群体适应性改编研究（2023）</v>
+        <v/>
       </c>
       <c r="Z2" t="str">
-        <v>主观压力值下降&gt;=1分；一周后情绪耗竭维度得分下降</v>
+        <v>A</v>
       </c>
       <c r="AA2" t="str">
-        <v>连续使用3次后主观压力值未下降</v>
+        <v>学习问题智能辅导系统 第2章</v>
       </c>
       <c r="AB2" t="str">
-        <v>确保教师有3分钟不被打扰的环境</v>
+        <v>五天内记录完整</v>
       </c>
       <c r="AC2" t="str">
-        <v>计时器、一周能量记录卡</v>
+        <v>记录不足三天</v>
       </c>
       <c r="AD2" t="str">
-        <v>一周能量记录卡</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE2" t="str">
-        <v>LP_RX_004</v>
+        <v>记录表</v>
       </c>
       <c r="AF2" t="str">
-        <v>学生学习问题处方库 P12</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+      <c r="AI2" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH2" t="str">
-        <v>class_system,home_school</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
         <v>LP_RX_002</v>
       </c>
       <c r="B3" t="str">
-        <v>错题分析模板</v>
+        <v>ZPD 教学支架卡</v>
       </c>
       <c r="C3" t="str">
-        <v>错题分析</v>
+        <v>ZPD支架</v>
       </c>
       <c r="D3" t="str">
         <v>learning_problem</v>
       </c>
       <c r="E3" t="str">
-        <v>worksheet</v>
+        <v>framework</v>
       </c>
       <c r="F3" t="str">
         <v>all</v>
@@ -632,46 +647,49 @@
         <v>teacher</v>
       </c>
       <c r="H3" t="str">
-        <v>日常自我照顾和压力管理</v>
+        <v>学生会做原题但不会变式时</v>
       </c>
       <c r="I3" t="str">
-        <v>low</v>
+        <v>high</v>
       </c>
       <c r="J3" t="str">
-        <v>作业完成度持续走低</v>
+        <v>LP_AT_COGNITION</v>
       </c>
       <c r="K3" t="str">
-        <v>learning_problem,yellow,analysis</v>
+        <v>认知加工困难</v>
       </c>
       <c r="L3" t="str">
-        <v>自我照顾</v>
+        <v>learning_problem,cognition</v>
       </c>
       <c r="M3" t="str">
-        <v>1) 记录每日能量变化 2) 识别能量消耗源 3) 制定能量补充计划</v>
+        <v>LP_COGNITION</v>
       </c>
       <c r="N3" t="str">
-        <v>记录本身就是一种觉察和关爱。</v>
-      </c>
-      <c r="O3" t="str">
-        <v>帮助教师建立自我照顾习惯，降低日常压力水平</v>
+        <v>在最近发展区内提供恰当强度的支持</v>
+      </c>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">确定目标和学生当前的实际水平
+判断两者之间的最近发展区
+从示范、提示、提问、同伴互助中选一种支架
+明确退出标准，逐步撤除支架</v>
       </c>
       <c r="P3" t="str">
-        <v>5 分钟</v>
+        <v>你先看我做一遍，然后我们一起做一遍，最后你自己做一遍。</v>
       </c>
       <c r="Q3" t="str">
-        <v>每日一次，持续 14 天</v>
+        <v>学生能独立完成一道变式题</v>
       </c>
       <c r="R3" t="str">
-        <v>14</v>
+        <v>一节课</v>
       </c>
       <c r="S3" t="str">
-        <v>本工具不适用于危机情境；教师处于急性心理危机时请先转介心理专员</v>
+        <v>每周两次</v>
       </c>
       <c r="T3" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U3" t="str">
-        <v/>
+        <v>不要直接给答案；不要跳过示范环节</v>
       </c>
       <c r="V3" t="str">
         <v/>
@@ -680,54 +698,60 @@
         <v/>
       </c>
       <c r="X3" t="str">
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y3" t="str">
-        <v>教师自我效能感训练研究（2022）</v>
+        <v/>
       </c>
       <c r="Z3" t="str">
-        <v>连续一周能量记录完整且主观压力值下降</v>
+        <v>A</v>
       </c>
       <c r="AA3" t="str">
-        <v>连续3天未记录</v>
+        <v>维果茨基理论的课堂应用</v>
       </c>
       <c r="AB3" t="str">
-        <v>打印一周能量记录卡</v>
+        <v>撤除支架后仍能完成</v>
       </c>
       <c r="AC3" t="str">
-        <v>一周能量记录卡、笔</v>
+        <v>三次后仍完全依赖支架</v>
       </c>
       <c r="AD3" t="str">
-        <v>完成的一周能量记录卡</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE3" t="str">
-        <v/>
+        <v>记录表</v>
       </c>
       <c r="AF3" t="str">
-        <v>学生学习问题处方库 P15</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+      <c r="AI3" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>LP_RX_003</v>
       </c>
       <c r="B4" t="str">
-        <v>学习策略训练</v>
+        <v>元认知提问清单</v>
       </c>
       <c r="C4" t="str">
-        <v>策略训练</v>
+        <v>元认知</v>
       </c>
       <c r="D4" t="str">
         <v>learning_problem</v>
       </c>
       <c r="E4" t="str">
-        <v>framework</v>
+        <v>checklist</v>
       </c>
       <c r="F4" t="str">
         <v>all</v>
@@ -736,46 +760,49 @@
         <v>teacher</v>
       </c>
       <c r="H4" t="str">
-        <v>需要同伴支持和经验交流时</v>
+        <v>学生独立解题时容易卡住</v>
       </c>
       <c r="I4" t="str">
-        <v>low</v>
+        <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>作业完成度持续走低</v>
+        <v>LP_AT_COGNITION</v>
       </c>
       <c r="K4" t="str">
-        <v>learning_problem,orange,strategy</v>
+        <v>认知加工困难</v>
       </c>
       <c r="L4" t="str">
-        <v>同伴支持</v>
+        <v>learning_problem,cognition</v>
       </c>
       <c r="M4" t="str">
-        <v>1) 邀请2-3位同事 2) 轮流分享当前困扰 3) 团体生成至少一条行动建议</v>
+        <v>LP_COGNITION</v>
       </c>
       <c r="N4" t="str">
-        <v>你不是一个人在战斗。</v>
-      </c>
-      <c r="O4" t="str">
-        <v>通过结构化同伴支持缓解教师的孤立感</v>
+        <v>把外部提示内化为自我提问习惯</v>
+      </c>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">给学生一张固定的四问清单：我要解决什么？我知道什么？我打算怎么做？做完怎么检查？
+前三次由教师带着问
+之后让学生自己对照清单出声说
+两周后撤掉清单，观察是否保留</v>
       </c>
       <c r="P4" t="str">
-        <v>30 分钟</v>
+        <v>先别急着算，你先说说这道题在问什么。</v>
       </c>
       <c r="Q4" t="str">
-        <v>每周一次，持续 4 周</v>
+        <v>学生能自主使用至少两个自我提问</v>
       </c>
       <c r="R4" t="str">
-        <v>28</v>
+        <v>10 分钟</v>
       </c>
       <c r="S4" t="str">
-        <v>本活动不等同于心理治疗，涉及严重心理问题时应转介专业支持</v>
+        <v>每次作业辅导时</v>
       </c>
       <c r="T4" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U4" t="str">
-        <v/>
+        <v>不要在学生思考时打断</v>
       </c>
       <c r="V4" t="str">
         <v/>
@@ -784,54 +811,60 @@
         <v/>
       </c>
       <c r="X4" t="str">
-        <v>C</v>
+        <v/>
       </c>
       <c r="Y4" t="str">
-        <v>同伴支持对教师职业倦怠干预效果研究（2021）</v>
+        <v/>
       </c>
       <c r="Z4" t="str">
-        <v>参与教师反馈压力感和孤立感下降</v>
+        <v>A</v>
       </c>
       <c r="AA4" t="str">
-        <v>连续2次参与人数低于2人</v>
+        <v>元认知策略教学研究</v>
       </c>
       <c r="AB4" t="str">
-        <v>准备问题引导卡</v>
+        <v>两周后能不看清单自问</v>
       </c>
       <c r="AC4" t="str">
-        <v>问题引导卡、白板、记号笔</v>
+        <v>两周后仍完全依赖提示</v>
       </c>
       <c r="AD4" t="str">
-        <v>行动建议记录表</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE4" t="str">
-        <v/>
+        <v>记录表</v>
       </c>
       <c r="AF4" t="str">
-        <v>学生学习问题处方库 P20</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+      <c r="AI4" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
+      <c r="AJ4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
         <v>LP_RX_004</v>
       </c>
       <c r="B5" t="str">
-        <v>课堂参与提升方案</v>
+        <v>课堂正向看见机会设计</v>
       </c>
       <c r="C5" t="str">
-        <v>参与提升</v>
+        <v>正向看见</v>
       </c>
       <c r="D5" t="str">
         <v>learning_problem</v>
       </c>
       <c r="E5" t="str">
-        <v>script</v>
+        <v>framework</v>
       </c>
       <c r="F5" t="str">
         <v>all</v>
@@ -840,97 +873,445 @@
         <v>teacher</v>
       </c>
       <c r="H5" t="str">
-        <v>出现明显负面自动思维时</v>
+        <v>学生因课堂归属感不足而回避学习</v>
       </c>
       <c r="I5" t="str">
         <v>medium</v>
       </c>
       <c r="J5" t="str">
-        <v>注意力与策略双重薄弱</v>
+        <v>LP_AT_RELATION</v>
       </c>
       <c r="K5" t="str">
-        <v>learning_problem,green,engagement</v>
+        <v>关系层影响</v>
       </c>
       <c r="L5" t="str">
-        <v>认知调整</v>
+        <v>learning_problem,relation</v>
       </c>
       <c r="M5" t="str">
-        <v>1) 识别负面自动思维 2) 检验思维的证据 3) 生成替代性解释 4) 行动计划</v>
+        <v>LP_RELATION</v>
       </c>
       <c r="N5" t="str">
-        <v>想法不一定是事实，让我们一起来看看证据。</v>
-      </c>
-      <c r="O5" t="str">
-        <v>帮助教师识别和调整负面自动思维，降低认知层面的压力</v>
+        <v>重建学生与课堂的正向联结</v>
+      </c>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">找一个该学生确定能答对的问题
+在课堂上点名请他回答
+肯定具体的思路而不是笼统说「很好」
+连续三次后观察其课堂参与变化</v>
       </c>
       <c r="P5" t="str">
+        <v>刚才他用的这个方法很关键，我们都跟着他的思路走一遍。</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>课堂主动参与次数增加</v>
+      </c>
+      <c r="R5" t="str">
+        <v>每次 2 分钟</v>
+      </c>
+      <c r="S5" t="str">
+        <v>每周三次，连续两周</v>
+      </c>
+      <c r="T5" t="str">
+        <v>30</v>
+      </c>
+      <c r="U5" t="str">
+        <v>不要设计明显降低难度的问题让其他学生看出来</v>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>课堂归属感与学业投入研究</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>两周内主动举手次数增加</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>两周后无变化</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>LP_RX_005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>自主任务选择卡</v>
+      </c>
+      <c r="C6" t="str">
+        <v>自主选择</v>
+      </c>
+      <c r="D6" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="E6" t="str">
+        <v>worksheet</v>
+      </c>
+      <c r="F6" t="str">
+        <v>all</v>
+      </c>
+      <c r="G6" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H6" t="str">
+        <v>学生完全依赖外部推动才学习</v>
+      </c>
+      <c r="I6" t="str">
+        <v>low</v>
+      </c>
+      <c r="J6" t="str">
+        <v>LP_AT_MOTIVATION</v>
+      </c>
+      <c r="K6" t="str">
+        <v>内驱动机不足</v>
+      </c>
+      <c r="L6" t="str">
+        <v>learning_problem,motivation</v>
+      </c>
+      <c r="M6" t="str">
+        <v>LP_INTRINSIC</v>
+      </c>
+      <c r="N6" t="str">
+        <v>通过给予选择权恢复自主感</v>
+      </c>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">给出三个难度相近但形式不同的任务选项
+让学生自己选一个并说明为什么选它
+让学生自己定义「做到什么程度算完成」
+完成后只针对他自己定的标准做反馈</v>
+      </c>
+      <c r="P6" t="str">
+        <v>这三个你挑一个，挑完告诉我你觉得做到什么程度算完成。</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>学生开始主动定义学习目标</v>
+      </c>
+      <c r="R6" t="str">
+        <v>10 分钟</v>
+      </c>
+      <c r="S6" t="str">
+        <v>每周一次</v>
+      </c>
+      <c r="T6" t="str">
+        <v>30</v>
+      </c>
+      <c r="U6" t="str">
+        <v>不要否定学生自定的完成标准</v>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>自我决定理论的课堂应用</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>学生能说出选择理由</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>连续两次拒绝选择</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG6" t="str">
+        <v/>
+      </c>
+      <c r="AH6" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+      <c r="AI6" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>LP_RX_006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>归因重塑最小任务</v>
+      </c>
+      <c r="C7" t="str">
+        <v>归因重塑</v>
+      </c>
+      <c r="D7" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="E7" t="str">
+        <v>exercise</v>
+      </c>
+      <c r="F7" t="str">
+        <v>all</v>
+      </c>
+      <c r="G7" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H7" t="str">
+        <v>学生认为「我就是学不会」时</v>
+      </c>
+      <c r="I7" t="str">
+        <v>high</v>
+      </c>
+      <c r="J7" t="str">
+        <v>LP_AT_EFFICACY</v>
+      </c>
+      <c r="K7" t="str">
+        <v>习得性无助</v>
+      </c>
+      <c r="L7" t="str">
+        <v>learning_problem,efficacy</v>
+      </c>
+      <c r="M7" t="str">
+        <v>LP_SELF_EFFICACY</v>
+      </c>
+      <c r="N7" t="str">
+        <v>把成功归因从能力转向方法</v>
+      </c>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">设计一个该学生必然能完成的最小任务
+完成后立刻问：「你觉得这次为什么做到了？」
+如果他答「运气好」或「题简单」，引导到具体方法上
+连续五次后回看，让他自己总结用过哪些方法</v>
+      </c>
+      <c r="P7" t="str">
+        <v>这次你先把题目读了两遍才动手，就是这一步让你没掉进坑里。</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>学生开始用方法解释成功</v>
+      </c>
+      <c r="R7" t="str">
         <v>15 分钟</v>
       </c>
-      <c r="Q5" t="str">
-        <v>每周 2-3 次，持续 4 周</v>
-      </c>
-      <c r="R5" t="str">
-        <v>14</v>
-      </c>
-      <c r="S5" t="str">
-        <v>有严重抑郁症状的教师应先在心理专员指导下使用</v>
-      </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str">
-        <v/>
-      </c>
-      <c r="V5" t="str">
-        <v/>
-      </c>
-      <c r="W5" t="str">
-        <v/>
-      </c>
-      <c r="X5" t="str">
+      <c r="S7" t="str">
+        <v>每周两次，连续三周</v>
+      </c>
+      <c r="T7" t="str">
+        <v>30</v>
+      </c>
+      <c r="U7" t="str">
+        <v>不要用「你很聪明」这类能力归因来鼓励</v>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>归因理论在学业干预中的应用</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>五次内出现方法归因</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>五次后仍归因于运气或难度</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+      <c r="AI7" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>LP_RX_007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>系统干预协同方案</v>
+      </c>
+      <c r="C8" t="str">
+        <v>系统干预</v>
+      </c>
+      <c r="D8" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="E8" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F8" t="str">
+        <v>all</v>
+      </c>
+      <c r="G8" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H8" t="str">
+        <v>三个层面同时受阻，单一措施无效时</v>
+      </c>
+      <c r="I8" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="J8" t="str">
+        <v>LP_AT_COGNITION</v>
+      </c>
+      <c r="K8" t="str">
+        <v>认知加工困难</v>
+      </c>
+      <c r="L8" t="str">
+        <v>learning_problem,cognition,crisis</v>
+      </c>
+      <c r="M8" t="str">
+        <v>LP_COGNITION</v>
+      </c>
+      <c r="N8" t="str">
+        <v>整合多方资源制定系统干预</v>
+      </c>
+      <c r="O8" t="str" xml:space="preserve">
+        <v xml:space="preserve">召集班主任、任课教师和家长做一次三方会商
+基于三层诊断结果确定一个主攻层面
+为每一方明确一项具体的支持动作和检查节点
+两周后复盘，只调整无效的那一项</v>
+      </c>
+      <c r="P8" t="str">
+        <v>我们这次不铺开做，只挑一个层面，两周后看效果再决定下一步。</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>形成一份三方共同承诺的干预计划</v>
+      </c>
+      <c r="R8" t="str">
+        <v>60 分钟</v>
+      </c>
+      <c r="S8" t="str">
+        <v>每两周复盘一次</v>
+      </c>
+      <c r="T8" t="str">
+        <v>30</v>
+      </c>
+      <c r="U8" t="str">
+        <v>不要同时启动超过三项措施</v>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
         <v>B</v>
       </c>
-      <c r="Y5" t="str">
-        <v>Beck 认知疗法教师适应性改编研究（2022）</v>
-      </c>
-      <c r="Z5" t="str">
-        <v>2周后负面自动思维频率下降 &gt;=30%</v>
-      </c>
-      <c r="AA5" t="str">
-        <v>使用2周后负面思维频率未下降且教师反馈无改善</v>
-      </c>
-      <c r="AB5" t="str">
-        <v>打印认知重构工作表</v>
-      </c>
-      <c r="AC5" t="str">
-        <v>认知重构工作表、笔</v>
-      </c>
-      <c r="AD5" t="str">
-        <v>完成的认知重构工作表</v>
-      </c>
-      <c r="AE5" t="str">
-        <v/>
-      </c>
-      <c r="AF5" t="str">
-        <v>学生学习问题处方库 P18</v>
-      </c>
-      <c r="AG5" t="str">
+      <c r="AA8" t="str">
+        <v>学习困难系统干预实务</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>三方均有明确动作和时限</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>任一方无法承诺具体动作</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG8" t="str">
+        <v/>
+      </c>
+      <c r="AH8" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+      <c r="AI8" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH5" t="str">
+      <c r="AJ8" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -972,28 +1353,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>离开当前情境</v>
+        <v>连续五天记录课堂参与、作</v>
       </c>
       <c r="D2" t="str">
-        <v>暂时离开当前工作环境（办公室、教室），找到一个安静不被打扰的空间</v>
+        <v>连续五天记录课堂参与、作业完成和测验表现三项</v>
       </c>
       <c r="E2" t="str">
-        <v>30秒</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>不需要走很远，去走廊尽头或空会议室即可</v>
+        <v>这一步决定后面能不能走下去</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>我注意到你在数学课的后半节特别容易走神，我们一起看看能怎么调整。</v>
       </c>
       <c r="I2" t="str">
-        <v>教师已经离开原环境，至少获得3分钟不被干扰的时间</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J2" t="str">
-        <v>如果实在无法离开怎么办？（答：至少转身背对工作区域，闭眼30秒）</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1004,28 +1385,28 @@
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>三轮缓慢呼吸</v>
+        <v>标出每天状态最好和最差的</v>
       </c>
       <c r="D3" t="str">
-        <v>进行三轮缓慢深呼吸：吸气4秒→屏息2秒→呼气6秒。每轮之间自然呼吸10秒</v>
+        <v>标出每天状态最好和最差的时段</v>
       </c>
       <c r="E3" t="str">
-        <v>60秒</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>计时器（可选）</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>不要刻意用力呼吸，重点是让呼气比吸气更长</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>完成了三轮呼吸</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J3" t="str">
-        <v>如果注意力无法集中怎么办？（答：把注意力放在呼气的感觉上，每次走神都重新回来即可）</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1036,25 +1417,25 @@
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>命名此刻的情绪</v>
+        <v>找出重复出现的模式，如某</v>
       </c>
       <c r="D4" t="str">
-        <v>问自己「我现在感受到的是什么？」——是愤怒、委屈、无力、焦虑、还是别的？给情绪一个名字</v>
+        <v>找出重复出现的模式，如某节课后必然分心</v>
       </c>
       <c r="E4" t="str">
-        <v>30秒</v>
+        <v/>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>不需要分析原因，只需要命名。如果同时有多种情绪，选最强烈的那一个</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>教师能够说出至少一种情绪的名称</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -1068,25 +1449,25 @@
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>选一个最小行动</v>
+        <v>针对最高频的模式做一次环</v>
       </c>
       <c r="D5" t="str">
-        <v>问自己「接下来5分钟，我能做的最小、最简单的一件事是什么？」选一件，然后做</v>
+        <v>针对最高频的模式做一次环境或任务调整</v>
       </c>
       <c r="E5" t="str">
-        <v>60秒</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>最小行动的标准：不需要别人配合，不需要准备，立即能做</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>教师选出了至少一个可行的最小行动</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -1100,25 +1481,25 @@
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>记录今日能量</v>
+        <v>确定目标和学生当前的实际</v>
       </c>
       <c r="D6" t="str">
-        <v>在能量记录卡上记录你今天几个关键时间点的能量状态（1-10分）</v>
+        <v>确定目标和学生当前的实际水平</v>
       </c>
       <c r="E6" t="str">
-        <v>3分钟</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>能量记录卡</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>保持诚实，不需要美化</v>
+        <v>这一步决定后面能不能走下去</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>你先看我做一遍，然后我们一起做一遍，最后你自己做一遍。</v>
       </c>
       <c r="I6" t="str">
-        <v>完成了至少3个时间点的记录</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1132,40 +1513,744 @@
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>识别能量消耗</v>
+        <v>判断两者之间的最近发展区</v>
       </c>
       <c r="D7" t="str">
-        <v>回顾今天的能量低谷，思考是什么消耗了你的能量</v>
+        <v>判断两者之间的最近发展区</v>
       </c>
       <c r="E7" t="str">
-        <v>2分钟</v>
+        <v/>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>不需要找出所有原因，选影响最大的1-2个即可</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>识别出至少1个能量消耗源</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LP_RX_002</v>
+      </c>
+      <c r="B8" t="str">
+        <v>3</v>
+      </c>
+      <c r="C8" t="str">
+        <v>从示范、提示、提问、同伴</v>
+      </c>
+      <c r="D8" t="str">
+        <v>从示范、提示、提问、同伴互助中选一种支架</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>LP_RX_002</v>
+      </c>
+      <c r="B9" t="str">
+        <v>4</v>
+      </c>
+      <c r="C9" t="str">
+        <v>明确退出标准，逐步撤除支</v>
+      </c>
+      <c r="D9" t="str">
+        <v>明确退出标准，逐步撤除支架</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LP_RX_003</v>
+      </c>
+      <c r="B10" t="str">
+        <v>1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>给学生一张固定的四问清单</v>
+      </c>
+      <c r="D10" t="str">
+        <v>给学生一张固定的四问清单：我要解决什么？我知道什么？我打算怎么做？做完怎么检查？</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H10" t="str">
+        <v>先别急着算，你先说说这道题在问什么。</v>
+      </c>
+      <c r="I10" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LP_RX_003</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2</v>
+      </c>
+      <c r="C11" t="str">
+        <v>前三次由教师带着问</v>
+      </c>
+      <c r="D11" t="str">
+        <v>前三次由教师带着问</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LP_RX_003</v>
+      </c>
+      <c r="B12" t="str">
+        <v>3</v>
+      </c>
+      <c r="C12" t="str">
+        <v>之后让学生自己对照清单出</v>
+      </c>
+      <c r="D12" t="str">
+        <v>之后让学生自己对照清单出声说</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LP_RX_003</v>
+      </c>
+      <c r="B13" t="str">
+        <v>4</v>
+      </c>
+      <c r="C13" t="str">
+        <v>两周后撤掉清单，观察是否</v>
+      </c>
+      <c r="D13" t="str">
+        <v>两周后撤掉清单，观察是否保留</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LP_RX_004</v>
+      </c>
+      <c r="B14" t="str">
+        <v>1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>找一个该学生确定能答对的</v>
+      </c>
+      <c r="D14" t="str">
+        <v>找一个该学生确定能答对的问题</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H14" t="str">
+        <v>刚才他用的这个方法很关键，我们都跟着他的思路走一遍。</v>
+      </c>
+      <c r="I14" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>LP_RX_004</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2</v>
+      </c>
+      <c r="C15" t="str">
+        <v>在课堂上点名请他回答</v>
+      </c>
+      <c r="D15" t="str">
+        <v>在课堂上点名请他回答</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>LP_RX_004</v>
+      </c>
+      <c r="B16" t="str">
+        <v>3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>肯定具体的思路而不是笼统</v>
+      </c>
+      <c r="D16" t="str">
+        <v>肯定具体的思路而不是笼统说「很好」</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>LP_RX_004</v>
+      </c>
+      <c r="B17" t="str">
+        <v>4</v>
+      </c>
+      <c r="C17" t="str">
+        <v>连续三次后观察其课堂参与</v>
+      </c>
+      <c r="D17" t="str">
+        <v>连续三次后观察其课堂参与变化</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>LP_RX_005</v>
+      </c>
+      <c r="B18" t="str">
+        <v>1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>给出三个难度相近但形式不</v>
+      </c>
+      <c r="D18" t="str">
+        <v>给出三个难度相近但形式不同的任务选项</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H18" t="str">
+        <v>这三个你挑一个，挑完告诉我你觉得做到什么程度算完成。</v>
+      </c>
+      <c r="I18" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>LP_RX_005</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2</v>
+      </c>
+      <c r="C19" t="str">
+        <v>让学生自己选一个并说明为</v>
+      </c>
+      <c r="D19" t="str">
+        <v>让学生自己选一个并说明为什么选它</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>LP_RX_005</v>
+      </c>
+      <c r="B20" t="str">
+        <v>3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>让学生自己定义「做到什么</v>
+      </c>
+      <c r="D20" t="str">
+        <v>让学生自己定义「做到什么程度算完成」</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>LP_RX_005</v>
+      </c>
+      <c r="B21" t="str">
+        <v>4</v>
+      </c>
+      <c r="C21" t="str">
+        <v>完成后只针对他自己定的标</v>
+      </c>
+      <c r="D21" t="str">
+        <v>完成后只针对他自己定的标准做反馈</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>LP_RX_006</v>
+      </c>
+      <c r="B22" t="str">
+        <v>1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>设计一个该学生必然能完成</v>
+      </c>
+      <c r="D22" t="str">
+        <v>设计一个该学生必然能完成的最小任务</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H22" t="str">
+        <v>这次你先把题目读了两遍才动手，就是这一步让你没掉进坑里。</v>
+      </c>
+      <c r="I22" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>LP_RX_006</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>完成后立刻问：「你觉得这</v>
+      </c>
+      <c r="D23" t="str">
+        <v>完成后立刻问：「你觉得这次为什么做到了？」</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>LP_RX_006</v>
+      </c>
+      <c r="B24" t="str">
+        <v>3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>如果他答「运气好」或「题</v>
+      </c>
+      <c r="D24" t="str">
+        <v>如果他答「运气好」或「题简单」，引导到具体方法上</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>LP_RX_006</v>
+      </c>
+      <c r="B25" t="str">
+        <v>4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>连续五次后回看，让他自己</v>
+      </c>
+      <c r="D25" t="str">
+        <v>连续五次后回看，让他自己总结用过哪些方法</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>LP_RX_007</v>
+      </c>
+      <c r="B26" t="str">
+        <v>1</v>
+      </c>
+      <c r="C26" t="str">
+        <v>召集班主任、任课教师和家</v>
+      </c>
+      <c r="D26" t="str">
+        <v>召集班主任、任课教师和家长做一次三方会商</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H26" t="str">
+        <v>我们这次不铺开做，只挑一个层面，两周后看效果再决定下一步。</v>
+      </c>
+      <c r="I26" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>LP_RX_007</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2</v>
+      </c>
+      <c r="C27" t="str">
+        <v>基于三层诊断结果确定一个</v>
+      </c>
+      <c r="D27" t="str">
+        <v>基于三层诊断结果确定一个主攻层面</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>LP_RX_007</v>
+      </c>
+      <c r="B28" t="str">
+        <v>3</v>
+      </c>
+      <c r="C28" t="str">
+        <v>为每一方明确一项具体的支</v>
+      </c>
+      <c r="D28" t="str">
+        <v>为每一方明确一项具体的支持动作和检查节点</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>LP_RX_007</v>
+      </c>
+      <c r="B29" t="str">
+        <v>4</v>
+      </c>
+      <c r="C29" t="str">
+        <v>两周后复盘，只调整无效的</v>
+      </c>
+      <c r="D29" t="str">
+        <v>两周后复盘，只调整无效的那一项</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J29" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J29"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1192,76 +2277,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_RX_001</v>
+        <v>LP_RX_007</v>
       </c>
       <c r="B2" t="str">
-        <v>教师自评抑郁量表得分&gt;=15</v>
+        <v>疑似存在学习障碍或注意力障碍</v>
       </c>
       <c r="C2" t="str">
-        <v>block</v>
+        <v>warn</v>
       </c>
       <c r="D2" t="str">
-        <v>抑郁风险较高时应先进行专业心理评估，不可单独依赖呼吸练习</v>
+        <v>教育干预无法替代专业评估</v>
       </c>
       <c r="E2" t="str">
-        <v>通知心理专员进行评估</v>
+        <v>建议家长带孩子到专业机构做评估，教育支持同步进行</v>
       </c>
       <c r="F2" t="str">
-        <v>存在抑郁风险的教师</v>
+        <v>班主任</v>
       </c>
       <c r="G2" t="str">
-        <v>PRD 8.2.1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>LP_RX_004</v>
-      </c>
-      <c r="B3" t="str">
-        <v>教师处于急性危机状态</v>
-      </c>
-      <c r="C3" t="str">
-        <v>block</v>
-      </c>
-      <c r="D3" t="str">
-        <v>急性危机时认知重构类工具可能加重混乱感</v>
-      </c>
-      <c r="E3" t="str">
-        <v>先使用安全稳定化工具，等状态稳定后再使用</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>PRD 8.2.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>LP_RX_003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>参与教师超过8人</v>
-      </c>
-      <c r="C4" t="str">
-        <v>warn</v>
-      </c>
-      <c r="D4" t="str">
-        <v>超过8人时小组讨论深度下降，建议拆分小组</v>
-      </c>
-      <c r="E4" t="str">
-        <v>每组控制在4-6人，增加一名引导员</v>
-      </c>
-      <c r="F4" t="str">
-        <v>年级组长</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
+        <v>学生学习问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/learning_problem/tool.xlsx
+++ b/business-libraries/test-data/learning_problem/tool.xlsx
@@ -511,15 +511,15 @@
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>LP_RX_001</v>
+        <v>LP_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>一周学习行为观察表</v>
       </c>
       <c r="C2" t="str">
-        <v>行为观察</v>
+        <v>一周学习行为观察</v>
       </c>
       <c r="D2" t="str">
         <v>learning_problem</v>
@@ -540,7 +540,7 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>LP_AT_BEHAVIOR</v>
+        <v>LP_AT_01</v>
       </c>
       <c r="K2" t="str">
         <v>学习行为失序</v>
@@ -549,16 +549,13 @@
         <v>learning_problem,behavior</v>
       </c>
       <c r="M2" t="str">
-        <v>LP_BEHAVIOR</v>
+        <v>LP_S1D1</v>
       </c>
       <c r="N2" t="str">
         <v>找出行为失序的具体模式和时段</v>
       </c>
-      <c r="O2" t="str" xml:space="preserve">
-        <v xml:space="preserve">连续五天记录课堂参与、作业完成和测验表现三项
-标出每天状态最好和最差的时段
-找出重复出现的模式，如某节课后必然分心
-针对最高频的模式做一次环境或任务调整</v>
+      <c r="O2" t="str">
+        <v>连续五天记录课堂参与、作业完成和测验表现三项；标出每天状态最好和最差的时段；找出重复出现的模式，如某节课后必然分心；针对最高频的模式做一次环境或任务调整</v>
       </c>
       <c r="P2" t="str">
         <v>我注意到你在数学课的后半节特别容易走神，我们一起看看能怎么调整。</v>
@@ -618,21 +615,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI2" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3" t="str">
-        <v>LP_RX_002</v>
+        <v>LP_RX_02</v>
       </c>
       <c r="B3" t="str">
         <v>ZPD 教学支架卡</v>
       </c>
       <c r="C3" t="str">
-        <v>ZPD支架</v>
+        <v>ZPD 教学支架</v>
       </c>
       <c r="D3" t="str">
         <v>learning_problem</v>
@@ -653,7 +650,7 @@
         <v>high</v>
       </c>
       <c r="J3" t="str">
-        <v>LP_AT_COGNITION</v>
+        <v>LP_AT_02</v>
       </c>
       <c r="K3" t="str">
         <v>认知加工困难</v>
@@ -662,16 +659,13 @@
         <v>learning_problem,cognition</v>
       </c>
       <c r="M3" t="str">
-        <v>LP_COGNITION</v>
+        <v>LP_S1D2</v>
       </c>
       <c r="N3" t="str">
         <v>在最近发展区内提供恰当强度的支持</v>
       </c>
-      <c r="O3" t="str" xml:space="preserve">
-        <v xml:space="preserve">确定目标和学生当前的实际水平
-判断两者之间的最近发展区
-从示范、提示、提问、同伴互助中选一种支架
-明确退出标准，逐步撤除支架</v>
+      <c r="O3" t="str">
+        <v>确定目标和学生当前的实际水平；判断两者之间的最近发展区；从示范、提示、提问、同伴互助中选一种支架；明确退出标准，逐步撤除支架</v>
       </c>
       <c r="P3" t="str">
         <v>你先看我做一遍，然后我们一起做一遍，最后你自己做一遍。</v>
@@ -731,21 +725,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI3" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4" t="str">
-        <v>LP_RX_003</v>
+        <v>LP_RX_03</v>
       </c>
       <c r="B4" t="str">
         <v>元认知提问清单</v>
       </c>
       <c r="C4" t="str">
-        <v>元认知</v>
+        <v>元认知提问清单</v>
       </c>
       <c r="D4" t="str">
         <v>learning_problem</v>
@@ -766,7 +760,7 @@
         <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>LP_AT_COGNITION</v>
+        <v>LP_AT_02</v>
       </c>
       <c r="K4" t="str">
         <v>认知加工困难</v>
@@ -775,16 +769,13 @@
         <v>learning_problem,cognition</v>
       </c>
       <c r="M4" t="str">
-        <v>LP_COGNITION</v>
+        <v>LP_S1D2</v>
       </c>
       <c r="N4" t="str">
         <v>把外部提示内化为自我提问习惯</v>
       </c>
-      <c r="O4" t="str" xml:space="preserve">
-        <v xml:space="preserve">给学生一张固定的四问清单：我要解决什么？我知道什么？我打算怎么做？做完怎么检查？
-前三次由教师带着问
-之后让学生自己对照清单出声说
-两周后撤掉清单，观察是否保留</v>
+      <c r="O4" t="str">
+        <v>给学生一张固定的四问清单：我要解决什么？我知道什么？我打算怎么做？做完怎么检查？；前三次由教师带着问；之后让学生自己对照清单出声说；两周后撤掉清单，观察是否保留</v>
       </c>
       <c r="P4" t="str">
         <v>先别急着算，你先说说这道题在问什么。</v>
@@ -844,21 +835,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI4" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5" t="str">
-        <v>LP_RX_004</v>
+        <v>LP_RX_04</v>
       </c>
       <c r="B5" t="str">
         <v>课堂正向看见机会设计</v>
       </c>
       <c r="C5" t="str">
-        <v>正向看见</v>
+        <v>课堂正向看见机会</v>
       </c>
       <c r="D5" t="str">
         <v>learning_problem</v>
@@ -879,7 +870,7 @@
         <v>medium</v>
       </c>
       <c r="J5" t="str">
-        <v>LP_AT_RELATION</v>
+        <v>LP_AT_03</v>
       </c>
       <c r="K5" t="str">
         <v>关系层影响</v>
@@ -888,16 +879,13 @@
         <v>learning_problem,relation</v>
       </c>
       <c r="M5" t="str">
-        <v>LP_RELATION</v>
+        <v>LP_S1D3</v>
       </c>
       <c r="N5" t="str">
         <v>重建学生与课堂的正向联结</v>
       </c>
-      <c r="O5" t="str" xml:space="preserve">
-        <v xml:space="preserve">找一个该学生确定能答对的问题
-在课堂上点名请他回答
-肯定具体的思路而不是笼统说「很好」
-连续三次后观察其课堂参与变化</v>
+      <c r="O5" t="str">
+        <v>找一个该学生确定能答对的问题；在课堂上点名请他回答；肯定具体的思路而不是笼统说「很好」；连续三次后观察其课堂参与变化</v>
       </c>
       <c r="P5" t="str">
         <v>刚才他用的这个方法很关键，我们都跟着他的思路走一遍。</v>
@@ -957,21 +945,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI5" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
+    <row r="6">
       <c r="A6" t="str">
-        <v>LP_RX_005</v>
+        <v>LP_RX_05</v>
       </c>
       <c r="B6" t="str">
         <v>自主任务选择卡</v>
       </c>
       <c r="C6" t="str">
-        <v>自主选择</v>
+        <v>自主任务选择卡</v>
       </c>
       <c r="D6" t="str">
         <v>learning_problem</v>
@@ -992,7 +980,7 @@
         <v>low</v>
       </c>
       <c r="J6" t="str">
-        <v>LP_AT_MOTIVATION</v>
+        <v>LP_AT_04</v>
       </c>
       <c r="K6" t="str">
         <v>内驱动机不足</v>
@@ -1001,16 +989,13 @@
         <v>learning_problem,motivation</v>
       </c>
       <c r="M6" t="str">
-        <v>LP_INTRINSIC</v>
+        <v>LP_S2D1</v>
       </c>
       <c r="N6" t="str">
         <v>通过给予选择权恢复自主感</v>
       </c>
-      <c r="O6" t="str" xml:space="preserve">
-        <v xml:space="preserve">给出三个难度相近但形式不同的任务选项
-让学生自己选一个并说明为什么选它
-让学生自己定义「做到什么程度算完成」
-完成后只针对他自己定的标准做反馈</v>
+      <c r="O6" t="str">
+        <v>给出三个难度相近但形式不同的任务选项；让学生自己选一个并说明为什么选它；让学生自己定义「做到什么程度算完成」；完成后只针对他自己定的标准做反馈</v>
       </c>
       <c r="P6" t="str">
         <v>这三个你挑一个，挑完告诉我你觉得做到什么程度算完成。</v>
@@ -1070,21 +1055,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI6" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
+    <row r="7">
       <c r="A7" t="str">
-        <v>LP_RX_006</v>
+        <v>LP_RX_06</v>
       </c>
       <c r="B7" t="str">
         <v>归因重塑最小任务</v>
       </c>
       <c r="C7" t="str">
-        <v>归因重塑</v>
+        <v>归因重塑最小任务</v>
       </c>
       <c r="D7" t="str">
         <v>learning_problem</v>
@@ -1105,7 +1090,7 @@
         <v>high</v>
       </c>
       <c r="J7" t="str">
-        <v>LP_AT_EFFICACY</v>
+        <v>LP_AT_05</v>
       </c>
       <c r="K7" t="str">
         <v>习得性无助</v>
@@ -1114,16 +1099,13 @@
         <v>learning_problem,efficacy</v>
       </c>
       <c r="M7" t="str">
-        <v>LP_SELF_EFFICACY</v>
+        <v>LP_S2D3</v>
       </c>
       <c r="N7" t="str">
         <v>把成功归因从能力转向方法</v>
       </c>
-      <c r="O7" t="str" xml:space="preserve">
-        <v xml:space="preserve">设计一个该学生必然能完成的最小任务
-完成后立刻问：「你觉得这次为什么做到了？」
-如果他答「运气好」或「题简单」，引导到具体方法上
-连续五次后回看，让他自己总结用过哪些方法</v>
+      <c r="O7" t="str">
+        <v>设计一个该学生必然能完成的最小任务；完成后立刻问：「你觉得这次为什么做到了？」；如果他答「运气好」或「题简单」，引导到具体方法上；连续五次后回看，让他自己总结用过哪些方法</v>
       </c>
       <c r="P7" t="str">
         <v>这次你先把题目读了两遍才动手，就是这一步让你没掉进坑里。</v>
@@ -1183,21 +1165,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI7" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
+    <row r="8">
       <c r="A8" t="str">
-        <v>LP_RX_007</v>
+        <v>LP_RX_07</v>
       </c>
       <c r="B8" t="str">
         <v>系统干预协同方案</v>
       </c>
       <c r="C8" t="str">
-        <v>系统干预</v>
+        <v>系统干预协同方案</v>
       </c>
       <c r="D8" t="str">
         <v>learning_problem</v>
@@ -1218,25 +1200,22 @@
         <v>crisis</v>
       </c>
       <c r="J8" t="str">
-        <v>LP_AT_COGNITION</v>
+        <v>LP_AT_02</v>
       </c>
       <c r="K8" t="str">
         <v>认知加工困难</v>
       </c>
       <c r="L8" t="str">
-        <v>learning_problem,cognition,crisis</v>
+        <v>learning_problem,cognition</v>
       </c>
       <c r="M8" t="str">
-        <v>LP_COGNITION</v>
+        <v>LP_S1D2</v>
       </c>
       <c r="N8" t="str">
         <v>整合多方资源制定系统干预</v>
       </c>
-      <c r="O8" t="str" xml:space="preserve">
-        <v xml:space="preserve">召集班主任、任课教师和家长做一次三方会商
-基于三层诊断结果确定一个主攻层面
-为每一方明确一项具体的支持动作和检查节点
-两周后复盘，只调整无效的那一项</v>
+      <c r="O8" t="str">
+        <v>召集班主任、任课教师和家长做一次三方会商；基于三层诊断结果确定一个主攻层面；为每一方明确一项具体的支持动作和检查节点；两周后复盘，只调整无效的那一项</v>
       </c>
       <c r="P8" t="str">
         <v>我们这次不铺开做，只挑一个层面，两周后看效果再决定下一步。</v>
@@ -1296,7 +1275,7 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI8" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ8" t="str">
         <v/>
@@ -1347,13 +1326,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_RX_001</v>
+        <v>LP_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>连续五天记录课堂参与、作</v>
+        <v>连续五天记录课堂参与、作业完成和测验表现三项</v>
       </c>
       <c r="D2" t="str">
         <v>连续五天记录课堂参与、作业完成和测验表现三项</v>
@@ -1379,13 +1358,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_RX_001</v>
+        <v>LP_RX_01</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>标出每天状态最好和最差的</v>
+        <v>标出每天状态最好和最差的时段</v>
       </c>
       <c r="D3" t="str">
         <v>标出每天状态最好和最差的时段</v>
@@ -1411,13 +1390,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_RX_001</v>
+        <v>LP_RX_01</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>找出重复出现的模式，如某</v>
+        <v>找出重复出现的模式，如某节课后必然分心</v>
       </c>
       <c r="D4" t="str">
         <v>找出重复出现的模式，如某节课后必然分心</v>
@@ -1443,13 +1422,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_RX_001</v>
+        <v>LP_RX_01</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>针对最高频的模式做一次环</v>
+        <v>针对最高频的模式做一次环境或任务调整</v>
       </c>
       <c r="D5" t="str">
         <v>针对最高频的模式做一次环境或任务调整</v>
@@ -1475,13 +1454,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_RX_002</v>
+        <v>LP_RX_02</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>确定目标和学生当前的实际</v>
+        <v>确定目标和学生当前的实际水平</v>
       </c>
       <c r="D6" t="str">
         <v>确定目标和学生当前的实际水平</v>
@@ -1507,7 +1486,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LP_RX_002</v>
+        <v>LP_RX_02</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
@@ -1539,13 +1518,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>LP_RX_002</v>
+        <v>LP_RX_02</v>
       </c>
       <c r="B8" t="str">
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>从示范、提示、提问、同伴</v>
+        <v>从示范、提示、提问、同伴互助中选一种支架</v>
       </c>
       <c r="D8" t="str">
         <v>从示范、提示、提问、同伴互助中选一种支架</v>
@@ -1571,13 +1550,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>LP_RX_002</v>
+        <v>LP_RX_02</v>
       </c>
       <c r="B9" t="str">
         <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>明确退出标准，逐步撤除支</v>
+        <v>明确退出标准，逐步撤除支架</v>
       </c>
       <c r="D9" t="str">
         <v>明确退出标准，逐步撤除支架</v>
@@ -1603,13 +1582,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LP_RX_003</v>
+        <v>LP_RX_03</v>
       </c>
       <c r="B10" t="str">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>给学生一张固定的四问清单</v>
+        <v>给学生一张固定的四问清单：我要解决什么？我知道什</v>
       </c>
       <c r="D10" t="str">
         <v>给学生一张固定的四问清单：我要解决什么？我知道什么？我打算怎么做？做完怎么检查？</v>
@@ -1635,7 +1614,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>LP_RX_003</v>
+        <v>LP_RX_03</v>
       </c>
       <c r="B11" t="str">
         <v>2</v>
@@ -1667,13 +1646,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>LP_RX_003</v>
+        <v>LP_RX_03</v>
       </c>
       <c r="B12" t="str">
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>之后让学生自己对照清单出</v>
+        <v>之后让学生自己对照清单出声说</v>
       </c>
       <c r="D12" t="str">
         <v>之后让学生自己对照清单出声说</v>
@@ -1699,13 +1678,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LP_RX_003</v>
+        <v>LP_RX_03</v>
       </c>
       <c r="B13" t="str">
         <v>4</v>
       </c>
       <c r="C13" t="str">
-        <v>两周后撤掉清单，观察是否</v>
+        <v>两周后撤掉清单，观察是否保留</v>
       </c>
       <c r="D13" t="str">
         <v>两周后撤掉清单，观察是否保留</v>
@@ -1731,13 +1710,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LP_RX_004</v>
+        <v>LP_RX_04</v>
       </c>
       <c r="B14" t="str">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>找一个该学生确定能答对的</v>
+        <v>找一个该学生确定能答对的问题</v>
       </c>
       <c r="D14" t="str">
         <v>找一个该学生确定能答对的问题</v>
@@ -1763,7 +1742,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>LP_RX_004</v>
+        <v>LP_RX_04</v>
       </c>
       <c r="B15" t="str">
         <v>2</v>
@@ -1795,13 +1774,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>LP_RX_004</v>
+        <v>LP_RX_04</v>
       </c>
       <c r="B16" t="str">
         <v>3</v>
       </c>
       <c r="C16" t="str">
-        <v>肯定具体的思路而不是笼统</v>
+        <v>肯定具体的思路而不是笼统说「很好」</v>
       </c>
       <c r="D16" t="str">
         <v>肯定具体的思路而不是笼统说「很好」</v>
@@ -1827,13 +1806,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>LP_RX_004</v>
+        <v>LP_RX_04</v>
       </c>
       <c r="B17" t="str">
         <v>4</v>
       </c>
       <c r="C17" t="str">
-        <v>连续三次后观察其课堂参与</v>
+        <v>连续三次后观察其课堂参与变化</v>
       </c>
       <c r="D17" t="str">
         <v>连续三次后观察其课堂参与变化</v>
@@ -1859,13 +1838,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>LP_RX_005</v>
+        <v>LP_RX_05</v>
       </c>
       <c r="B18" t="str">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>给出三个难度相近但形式不</v>
+        <v>给出三个难度相近但形式不同的任务选项</v>
       </c>
       <c r="D18" t="str">
         <v>给出三个难度相近但形式不同的任务选项</v>
@@ -1891,13 +1870,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>LP_RX_005</v>
+        <v>LP_RX_05</v>
       </c>
       <c r="B19" t="str">
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>让学生自己选一个并说明为</v>
+        <v>让学生自己选一个并说明为什么选它</v>
       </c>
       <c r="D19" t="str">
         <v>让学生自己选一个并说明为什么选它</v>
@@ -1923,13 +1902,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>LP_RX_005</v>
+        <v>LP_RX_05</v>
       </c>
       <c r="B20" t="str">
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>让学生自己定义「做到什么</v>
+        <v>让学生自己定义「做到什么程度算完成」</v>
       </c>
       <c r="D20" t="str">
         <v>让学生自己定义「做到什么程度算完成」</v>
@@ -1955,13 +1934,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>LP_RX_005</v>
+        <v>LP_RX_05</v>
       </c>
       <c r="B21" t="str">
         <v>4</v>
       </c>
       <c r="C21" t="str">
-        <v>完成后只针对他自己定的标</v>
+        <v>完成后只针对他自己定的标准做反馈</v>
       </c>
       <c r="D21" t="str">
         <v>完成后只针对他自己定的标准做反馈</v>
@@ -1987,13 +1966,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>LP_RX_006</v>
+        <v>LP_RX_06</v>
       </c>
       <c r="B22" t="str">
         <v>1</v>
       </c>
       <c r="C22" t="str">
-        <v>设计一个该学生必然能完成</v>
+        <v>设计一个该学生必然能完成的最小任务</v>
       </c>
       <c r="D22" t="str">
         <v>设计一个该学生必然能完成的最小任务</v>
@@ -2019,13 +1998,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>LP_RX_006</v>
+        <v>LP_RX_06</v>
       </c>
       <c r="B23" t="str">
         <v>2</v>
       </c>
       <c r="C23" t="str">
-        <v>完成后立刻问：「你觉得这</v>
+        <v>完成后立刻问：「你觉得这次为什么做到了？」</v>
       </c>
       <c r="D23" t="str">
         <v>完成后立刻问：「你觉得这次为什么做到了？」</v>
@@ -2051,13 +2030,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>LP_RX_006</v>
+        <v>LP_RX_06</v>
       </c>
       <c r="B24" t="str">
         <v>3</v>
       </c>
       <c r="C24" t="str">
-        <v>如果他答「运气好」或「题</v>
+        <v>如果他答「运气好」或「题简单」，引导到具体方法上</v>
       </c>
       <c r="D24" t="str">
         <v>如果他答「运气好」或「题简单」，引导到具体方法上</v>
@@ -2083,13 +2062,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>LP_RX_006</v>
+        <v>LP_RX_06</v>
       </c>
       <c r="B25" t="str">
         <v>4</v>
       </c>
       <c r="C25" t="str">
-        <v>连续五次后回看，让他自己</v>
+        <v>连续五次后回看，让他自己总结用过哪些方法</v>
       </c>
       <c r="D25" t="str">
         <v>连续五次后回看，让他自己总结用过哪些方法</v>
@@ -2115,13 +2094,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>LP_RX_007</v>
+        <v>LP_RX_07</v>
       </c>
       <c r="B26" t="str">
         <v>1</v>
       </c>
       <c r="C26" t="str">
-        <v>召集班主任、任课教师和家</v>
+        <v>召集班主任、任课教师和家长做一次三方会商</v>
       </c>
       <c r="D26" t="str">
         <v>召集班主任、任课教师和家长做一次三方会商</v>
@@ -2147,13 +2126,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>LP_RX_007</v>
+        <v>LP_RX_07</v>
       </c>
       <c r="B27" t="str">
         <v>2</v>
       </c>
       <c r="C27" t="str">
-        <v>基于三层诊断结果确定一个</v>
+        <v>基于三层诊断结果确定一个主攻层面</v>
       </c>
       <c r="D27" t="str">
         <v>基于三层诊断结果确定一个主攻层面</v>
@@ -2179,13 +2158,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>LP_RX_007</v>
+        <v>LP_RX_07</v>
       </c>
       <c r="B28" t="str">
         <v>3</v>
       </c>
       <c r="C28" t="str">
-        <v>为每一方明确一项具体的支</v>
+        <v>为每一方明确一项具体的支持动作和检查节点</v>
       </c>
       <c r="D28" t="str">
         <v>为每一方明确一项具体的支持动作和检查节点</v>
@@ -2211,13 +2190,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>LP_RX_007</v>
+        <v>LP_RX_07</v>
       </c>
       <c r="B29" t="str">
         <v>4</v>
       </c>
       <c r="C29" t="str">
-        <v>两周后复盘，只调整无效的</v>
+        <v>两周后复盘，只调整无效的那一项</v>
       </c>
       <c r="D29" t="str">
         <v>两周后复盘，只调整无效的那一项</v>
@@ -2277,7 +2256,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_RX_007</v>
+        <v>LP_RX_07</v>
       </c>
       <c r="B2" t="str">
         <v>疑似存在学习障碍或注意力障碍</v>

--- a/business-libraries/test-data/learning_problem/tool.xlsx
+++ b/business-libraries/test-data/learning_problem/tool.xlsx
@@ -511,15 +511,15 @@
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>LP_RX_01</v>
+        <v>LP_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>一周学习行为观察表</v>
       </c>
       <c r="C2" t="str">
-        <v>一周学习行为观察</v>
+        <v>行为观察</v>
       </c>
       <c r="D2" t="str">
         <v>learning_problem</v>
@@ -540,7 +540,7 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>LP_AT_01</v>
+        <v>LP_AT_BEHAVIOR</v>
       </c>
       <c r="K2" t="str">
         <v>学习行为失序</v>
@@ -549,13 +549,16 @@
         <v>learning_problem,behavior</v>
       </c>
       <c r="M2" t="str">
-        <v>LP_S1D1</v>
+        <v>LP_BEHAVIOR</v>
       </c>
       <c r="N2" t="str">
         <v>找出行为失序的具体模式和时段</v>
       </c>
-      <c r="O2" t="str">
-        <v>连续五天记录课堂参与、作业完成和测验表现三项；标出每天状态最好和最差的时段；找出重复出现的模式，如某节课后必然分心；针对最高频的模式做一次环境或任务调整</v>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">连续五天记录课堂参与、作业完成和测验表现三项
+标出每天状态最好和最差的时段
+找出重复出现的模式，如某节课后必然分心
+针对最高频的模式做一次环境或任务调整</v>
       </c>
       <c r="P2" t="str">
         <v>我注意到你在数学课的后半节特别容易走神，我们一起看看能怎么调整。</v>
@@ -615,21 +618,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI2" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>LP_RX_02</v>
+        <v>LP_RX_002</v>
       </c>
       <c r="B3" t="str">
         <v>ZPD 教学支架卡</v>
       </c>
       <c r="C3" t="str">
-        <v>ZPD 教学支架</v>
+        <v>ZPD支架</v>
       </c>
       <c r="D3" t="str">
         <v>learning_problem</v>
@@ -650,7 +653,7 @@
         <v>high</v>
       </c>
       <c r="J3" t="str">
-        <v>LP_AT_02</v>
+        <v>LP_AT_COGNITION</v>
       </c>
       <c r="K3" t="str">
         <v>认知加工困难</v>
@@ -659,13 +662,16 @@
         <v>learning_problem,cognition</v>
       </c>
       <c r="M3" t="str">
-        <v>LP_S1D2</v>
+        <v>LP_COGNITION</v>
       </c>
       <c r="N3" t="str">
         <v>在最近发展区内提供恰当强度的支持</v>
       </c>
-      <c r="O3" t="str">
-        <v>确定目标和学生当前的实际水平；判断两者之间的最近发展区；从示范、提示、提问、同伴互助中选一种支架；明确退出标准，逐步撤除支架</v>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">确定目标和学生当前的实际水平
+判断两者之间的最近发展区
+从示范、提示、提问、同伴互助中选一种支架
+明确退出标准，逐步撤除支架</v>
       </c>
       <c r="P3" t="str">
         <v>你先看我做一遍，然后我们一起做一遍，最后你自己做一遍。</v>
@@ -725,21 +731,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI3" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>LP_RX_03</v>
+        <v>LP_RX_003</v>
       </c>
       <c r="B4" t="str">
         <v>元认知提问清单</v>
       </c>
       <c r="C4" t="str">
-        <v>元认知提问清单</v>
+        <v>元认知</v>
       </c>
       <c r="D4" t="str">
         <v>learning_problem</v>
@@ -760,7 +766,7 @@
         <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>LP_AT_02</v>
+        <v>LP_AT_COGNITION</v>
       </c>
       <c r="K4" t="str">
         <v>认知加工困难</v>
@@ -769,13 +775,16 @@
         <v>learning_problem,cognition</v>
       </c>
       <c r="M4" t="str">
-        <v>LP_S1D2</v>
+        <v>LP_COGNITION</v>
       </c>
       <c r="N4" t="str">
         <v>把外部提示内化为自我提问习惯</v>
       </c>
-      <c r="O4" t="str">
-        <v>给学生一张固定的四问清单：我要解决什么？我知道什么？我打算怎么做？做完怎么检查？；前三次由教师带着问；之后让学生自己对照清单出声说；两周后撤掉清单，观察是否保留</v>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">给学生一张固定的四问清单：我要解决什么？我知道什么？我打算怎么做？做完怎么检查？
+前三次由教师带着问
+之后让学生自己对照清单出声说
+两周后撤掉清单，观察是否保留</v>
       </c>
       <c r="P4" t="str">
         <v>先别急着算，你先说说这道题在问什么。</v>
@@ -835,21 +844,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI4" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>LP_RX_04</v>
+        <v>LP_RX_004</v>
       </c>
       <c r="B5" t="str">
         <v>课堂正向看见机会设计</v>
       </c>
       <c r="C5" t="str">
-        <v>课堂正向看见机会</v>
+        <v>正向看见</v>
       </c>
       <c r="D5" t="str">
         <v>learning_problem</v>
@@ -870,7 +879,7 @@
         <v>medium</v>
       </c>
       <c r="J5" t="str">
-        <v>LP_AT_03</v>
+        <v>LP_AT_RELATION</v>
       </c>
       <c r="K5" t="str">
         <v>关系层影响</v>
@@ -879,13 +888,16 @@
         <v>learning_problem,relation</v>
       </c>
       <c r="M5" t="str">
-        <v>LP_S1D3</v>
+        <v>LP_RELATION</v>
       </c>
       <c r="N5" t="str">
         <v>重建学生与课堂的正向联结</v>
       </c>
-      <c r="O5" t="str">
-        <v>找一个该学生确定能答对的问题；在课堂上点名请他回答；肯定具体的思路而不是笼统说「很好」；连续三次后观察其课堂参与变化</v>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">找一个该学生确定能答对的问题
+在课堂上点名请他回答
+肯定具体的思路而不是笼统说「很好」
+连续三次后观察其课堂参与变化</v>
       </c>
       <c r="P5" t="str">
         <v>刚才他用的这个方法很关键，我们都跟着他的思路走一遍。</v>
@@ -945,21 +957,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI5" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>LP_RX_05</v>
+        <v>LP_RX_005</v>
       </c>
       <c r="B6" t="str">
         <v>自主任务选择卡</v>
       </c>
       <c r="C6" t="str">
-        <v>自主任务选择卡</v>
+        <v>自主选择</v>
       </c>
       <c r="D6" t="str">
         <v>learning_problem</v>
@@ -980,7 +992,7 @@
         <v>low</v>
       </c>
       <c r="J6" t="str">
-        <v>LP_AT_04</v>
+        <v>LP_AT_MOTIVATION</v>
       </c>
       <c r="K6" t="str">
         <v>内驱动机不足</v>
@@ -989,13 +1001,16 @@
         <v>learning_problem,motivation</v>
       </c>
       <c r="M6" t="str">
-        <v>LP_S2D1</v>
+        <v>LP_INTRINSIC</v>
       </c>
       <c r="N6" t="str">
         <v>通过给予选择权恢复自主感</v>
       </c>
-      <c r="O6" t="str">
-        <v>给出三个难度相近但形式不同的任务选项；让学生自己选一个并说明为什么选它；让学生自己定义「做到什么程度算完成」；完成后只针对他自己定的标准做反馈</v>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">给出三个难度相近但形式不同的任务选项
+让学生自己选一个并说明为什么选它
+让学生自己定义「做到什么程度算完成」
+完成后只针对他自己定的标准做反馈</v>
       </c>
       <c r="P6" t="str">
         <v>这三个你挑一个，挑完告诉我你觉得做到什么程度算完成。</v>
@@ -1055,21 +1070,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI6" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>LP_RX_06</v>
+        <v>LP_RX_006</v>
       </c>
       <c r="B7" t="str">
         <v>归因重塑最小任务</v>
       </c>
       <c r="C7" t="str">
-        <v>归因重塑最小任务</v>
+        <v>归因重塑</v>
       </c>
       <c r="D7" t="str">
         <v>learning_problem</v>
@@ -1090,7 +1105,7 @@
         <v>high</v>
       </c>
       <c r="J7" t="str">
-        <v>LP_AT_05</v>
+        <v>LP_AT_EFFICACY</v>
       </c>
       <c r="K7" t="str">
         <v>习得性无助</v>
@@ -1099,13 +1114,16 @@
         <v>learning_problem,efficacy</v>
       </c>
       <c r="M7" t="str">
-        <v>LP_S2D3</v>
+        <v>LP_SELF_EFFICACY</v>
       </c>
       <c r="N7" t="str">
         <v>把成功归因从能力转向方法</v>
       </c>
-      <c r="O7" t="str">
-        <v>设计一个该学生必然能完成的最小任务；完成后立刻问：「你觉得这次为什么做到了？」；如果他答「运气好」或「题简单」，引导到具体方法上；连续五次后回看，让他自己总结用过哪些方法</v>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">设计一个该学生必然能完成的最小任务
+完成后立刻问：「你觉得这次为什么做到了？」
+如果他答「运气好」或「题简单」，引导到具体方法上
+连续五次后回看，让他自己总结用过哪些方法</v>
       </c>
       <c r="P7" t="str">
         <v>这次你先把题目读了两遍才动手，就是这一步让你没掉进坑里。</v>
@@ -1165,21 +1183,21 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI7" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>LP_RX_07</v>
+        <v>LP_RX_007</v>
       </c>
       <c r="B8" t="str">
         <v>系统干预协同方案</v>
       </c>
       <c r="C8" t="str">
-        <v>系统干预协同方案</v>
+        <v>系统干预</v>
       </c>
       <c r="D8" t="str">
         <v>learning_problem</v>
@@ -1200,22 +1218,25 @@
         <v>crisis</v>
       </c>
       <c r="J8" t="str">
-        <v>LP_AT_02</v>
+        <v>LP_AT_COGNITION</v>
       </c>
       <c r="K8" t="str">
         <v>认知加工困难</v>
       </c>
       <c r="L8" t="str">
-        <v>learning_problem,cognition</v>
+        <v>learning_problem,cognition,crisis</v>
       </c>
       <c r="M8" t="str">
-        <v>LP_S1D2</v>
+        <v>LP_COGNITION</v>
       </c>
       <c r="N8" t="str">
         <v>整合多方资源制定系统干预</v>
       </c>
-      <c r="O8" t="str">
-        <v>召集班主任、任课教师和家长做一次三方会商；基于三层诊断结果确定一个主攻层面；为每一方明确一项具体的支持动作和检查节点；两周后复盘，只调整无效的那一项</v>
+      <c r="O8" t="str" xml:space="preserve">
+        <v xml:space="preserve">召集班主任、任课教师和家长做一次三方会商
+基于三层诊断结果确定一个主攻层面
+为每一方明确一项具体的支持动作和检查节点
+两周后复盘，只调整无效的那一项</v>
       </c>
       <c r="P8" t="str">
         <v>我们这次不铺开做，只挑一个层面，两周后看效果再决定下一步。</v>
@@ -1275,7 +1296,7 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AI8" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ8" t="str">
         <v/>
@@ -1326,13 +1347,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_RX_01</v>
+        <v>LP_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>连续五天记录课堂参与、作业完成和测验表现三项</v>
+        <v>连续五天记录课堂参与、作</v>
       </c>
       <c r="D2" t="str">
         <v>连续五天记录课堂参与、作业完成和测验表现三项</v>
@@ -1358,13 +1379,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_RX_01</v>
+        <v>LP_RX_001</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>标出每天状态最好和最差的时段</v>
+        <v>标出每天状态最好和最差的</v>
       </c>
       <c r="D3" t="str">
         <v>标出每天状态最好和最差的时段</v>
@@ -1390,13 +1411,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_RX_01</v>
+        <v>LP_RX_001</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>找出重复出现的模式，如某节课后必然分心</v>
+        <v>找出重复出现的模式，如某</v>
       </c>
       <c r="D4" t="str">
         <v>找出重复出现的模式，如某节课后必然分心</v>
@@ -1422,13 +1443,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_RX_01</v>
+        <v>LP_RX_001</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>针对最高频的模式做一次环境或任务调整</v>
+        <v>针对最高频的模式做一次环</v>
       </c>
       <c r="D5" t="str">
         <v>针对最高频的模式做一次环境或任务调整</v>
@@ -1454,13 +1475,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_RX_02</v>
+        <v>LP_RX_002</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>确定目标和学生当前的实际水平</v>
+        <v>确定目标和学生当前的实际</v>
       </c>
       <c r="D6" t="str">
         <v>确定目标和学生当前的实际水平</v>
@@ -1486,7 +1507,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LP_RX_02</v>
+        <v>LP_RX_002</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
@@ -1518,13 +1539,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>LP_RX_02</v>
+        <v>LP_RX_002</v>
       </c>
       <c r="B8" t="str">
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>从示范、提示、提问、同伴互助中选一种支架</v>
+        <v>从示范、提示、提问、同伴</v>
       </c>
       <c r="D8" t="str">
         <v>从示范、提示、提问、同伴互助中选一种支架</v>
@@ -1550,13 +1571,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>LP_RX_02</v>
+        <v>LP_RX_002</v>
       </c>
       <c r="B9" t="str">
         <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>明确退出标准，逐步撤除支架</v>
+        <v>明确退出标准，逐步撤除支</v>
       </c>
       <c r="D9" t="str">
         <v>明确退出标准，逐步撤除支架</v>
@@ -1582,13 +1603,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LP_RX_03</v>
+        <v>LP_RX_003</v>
       </c>
       <c r="B10" t="str">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>给学生一张固定的四问清单：我要解决什么？我知道什</v>
+        <v>给学生一张固定的四问清单</v>
       </c>
       <c r="D10" t="str">
         <v>给学生一张固定的四问清单：我要解决什么？我知道什么？我打算怎么做？做完怎么检查？</v>
@@ -1614,7 +1635,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>LP_RX_03</v>
+        <v>LP_RX_003</v>
       </c>
       <c r="B11" t="str">
         <v>2</v>
@@ -1646,13 +1667,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>LP_RX_03</v>
+        <v>LP_RX_003</v>
       </c>
       <c r="B12" t="str">
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>之后让学生自己对照清单出声说</v>
+        <v>之后让学生自己对照清单出</v>
       </c>
       <c r="D12" t="str">
         <v>之后让学生自己对照清单出声说</v>
@@ -1678,13 +1699,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LP_RX_03</v>
+        <v>LP_RX_003</v>
       </c>
       <c r="B13" t="str">
         <v>4</v>
       </c>
       <c r="C13" t="str">
-        <v>两周后撤掉清单，观察是否保留</v>
+        <v>两周后撤掉清单，观察是否</v>
       </c>
       <c r="D13" t="str">
         <v>两周后撤掉清单，观察是否保留</v>
@@ -1710,13 +1731,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LP_RX_04</v>
+        <v>LP_RX_004</v>
       </c>
       <c r="B14" t="str">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>找一个该学生确定能答对的问题</v>
+        <v>找一个该学生确定能答对的</v>
       </c>
       <c r="D14" t="str">
         <v>找一个该学生确定能答对的问题</v>
@@ -1742,7 +1763,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>LP_RX_04</v>
+        <v>LP_RX_004</v>
       </c>
       <c r="B15" t="str">
         <v>2</v>
@@ -1774,13 +1795,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>LP_RX_04</v>
+        <v>LP_RX_004</v>
       </c>
       <c r="B16" t="str">
         <v>3</v>
       </c>
       <c r="C16" t="str">
-        <v>肯定具体的思路而不是笼统说「很好」</v>
+        <v>肯定具体的思路而不是笼统</v>
       </c>
       <c r="D16" t="str">
         <v>肯定具体的思路而不是笼统说「很好」</v>
@@ -1806,13 +1827,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>LP_RX_04</v>
+        <v>LP_RX_004</v>
       </c>
       <c r="B17" t="str">
         <v>4</v>
       </c>
       <c r="C17" t="str">
-        <v>连续三次后观察其课堂参与变化</v>
+        <v>连续三次后观察其课堂参与</v>
       </c>
       <c r="D17" t="str">
         <v>连续三次后观察其课堂参与变化</v>
@@ -1838,13 +1859,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>LP_RX_05</v>
+        <v>LP_RX_005</v>
       </c>
       <c r="B18" t="str">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>给出三个难度相近但形式不同的任务选项</v>
+        <v>给出三个难度相近但形式不</v>
       </c>
       <c r="D18" t="str">
         <v>给出三个难度相近但形式不同的任务选项</v>
@@ -1870,13 +1891,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>LP_RX_05</v>
+        <v>LP_RX_005</v>
       </c>
       <c r="B19" t="str">
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>让学生自己选一个并说明为什么选它</v>
+        <v>让学生自己选一个并说明为</v>
       </c>
       <c r="D19" t="str">
         <v>让学生自己选一个并说明为什么选它</v>
@@ -1902,13 +1923,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>LP_RX_05</v>
+        <v>LP_RX_005</v>
       </c>
       <c r="B20" t="str">
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>让学生自己定义「做到什么程度算完成」</v>
+        <v>让学生自己定义「做到什么</v>
       </c>
       <c r="D20" t="str">
         <v>让学生自己定义「做到什么程度算完成」</v>
@@ -1934,13 +1955,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>LP_RX_05</v>
+        <v>LP_RX_005</v>
       </c>
       <c r="B21" t="str">
         <v>4</v>
       </c>
       <c r="C21" t="str">
-        <v>完成后只针对他自己定的标准做反馈</v>
+        <v>完成后只针对他自己定的标</v>
       </c>
       <c r="D21" t="str">
         <v>完成后只针对他自己定的标准做反馈</v>
@@ -1966,13 +1987,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>LP_RX_06</v>
+        <v>LP_RX_006</v>
       </c>
       <c r="B22" t="str">
         <v>1</v>
       </c>
       <c r="C22" t="str">
-        <v>设计一个该学生必然能完成的最小任务</v>
+        <v>设计一个该学生必然能完成</v>
       </c>
       <c r="D22" t="str">
         <v>设计一个该学生必然能完成的最小任务</v>
@@ -1998,13 +2019,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>LP_RX_06</v>
+        <v>LP_RX_006</v>
       </c>
       <c r="B23" t="str">
         <v>2</v>
       </c>
       <c r="C23" t="str">
-        <v>完成后立刻问：「你觉得这次为什么做到了？」</v>
+        <v>完成后立刻问：「你觉得这</v>
       </c>
       <c r="D23" t="str">
         <v>完成后立刻问：「你觉得这次为什么做到了？」</v>
@@ -2030,13 +2051,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>LP_RX_06</v>
+        <v>LP_RX_006</v>
       </c>
       <c r="B24" t="str">
         <v>3</v>
       </c>
       <c r="C24" t="str">
-        <v>如果他答「运气好」或「题简单」，引导到具体方法上</v>
+        <v>如果他答「运气好」或「题</v>
       </c>
       <c r="D24" t="str">
         <v>如果他答「运气好」或「题简单」，引导到具体方法上</v>
@@ -2062,13 +2083,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>LP_RX_06</v>
+        <v>LP_RX_006</v>
       </c>
       <c r="B25" t="str">
         <v>4</v>
       </c>
       <c r="C25" t="str">
-        <v>连续五次后回看，让他自己总结用过哪些方法</v>
+        <v>连续五次后回看，让他自己</v>
       </c>
       <c r="D25" t="str">
         <v>连续五次后回看，让他自己总结用过哪些方法</v>
@@ -2094,13 +2115,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>LP_RX_07</v>
+        <v>LP_RX_007</v>
       </c>
       <c r="B26" t="str">
         <v>1</v>
       </c>
       <c r="C26" t="str">
-        <v>召集班主任、任课教师和家长做一次三方会商</v>
+        <v>召集班主任、任课教师和家</v>
       </c>
       <c r="D26" t="str">
         <v>召集班主任、任课教师和家长做一次三方会商</v>
@@ -2126,13 +2147,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>LP_RX_07</v>
+        <v>LP_RX_007</v>
       </c>
       <c r="B27" t="str">
         <v>2</v>
       </c>
       <c r="C27" t="str">
-        <v>基于三层诊断结果确定一个主攻层面</v>
+        <v>基于三层诊断结果确定一个</v>
       </c>
       <c r="D27" t="str">
         <v>基于三层诊断结果确定一个主攻层面</v>
@@ -2158,13 +2179,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>LP_RX_07</v>
+        <v>LP_RX_007</v>
       </c>
       <c r="B28" t="str">
         <v>3</v>
       </c>
       <c r="C28" t="str">
-        <v>为每一方明确一项具体的支持动作和检查节点</v>
+        <v>为每一方明确一项具体的支</v>
       </c>
       <c r="D28" t="str">
         <v>为每一方明确一项具体的支持动作和检查节点</v>
@@ -2190,13 +2211,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>LP_RX_07</v>
+        <v>LP_RX_007</v>
       </c>
       <c r="B29" t="str">
         <v>4</v>
       </c>
       <c r="C29" t="str">
-        <v>两周后复盘，只调整无效的那一项</v>
+        <v>两周后复盘，只调整无效的</v>
       </c>
       <c r="D29" t="str">
         <v>两周后复盘，只调整无效的那一项</v>
@@ -2256,7 +2277,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_RX_07</v>
+        <v>LP_RX_007</v>
       </c>
       <c r="B2" t="str">
         <v>疑似存在学习障碍或注意力障碍</v>
